--- a/tests/realSuite/Piano-Viaggi_Orienteering_15-aprile-2026_def/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Orienteering_15-aprile-2026_def/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,555 +451,645 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC ALTA VAL DI SOLE</t>
+          <t>IC ALDENO MATTARELLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Via S. Michele, 11 – Fucine di Ossana</t>
+          <t>Via Torre Franca – Fermata Bus "Al Parco" Mattarello</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC CEMBRA</t>
+          <t>IC ALTA VAL DI SOLE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Via al Grec, 2 - Giovo</t>
+          <t>Via S. Michele, 11 – Fucine di Ossana</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC CENTRO VALSUGANA</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fermata Bus "Pizzeria il Picchio" - Roncegno</t>
+          <t>Frazione Scancio 69 – Fermata Bus - Segonzano</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC CENTRO VALSUGANA</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fermata Bus Piazza Maggiore - Telve</t>
+          <t>Via Negritelle 1 - Cembra</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC CIVEZZANO</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Park Supermercato Lidl - Civezzano</t>
+          <t>Via al Grec, 2 - Giovo</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC GIUDICARIE ESTERIORI</t>
+          <t>IC CENTRO VALSUGANA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Via San Giovanni Bosco, 14 - Comano Terme</t>
+          <t>Fermata Bus "Pizzeria il Picchio" - Roncegno</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC LEVICO TERME</t>
+          <t>IC CENTRO VALSUGANA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Via della Pace, 5 – Levico Terme</t>
+          <t>Fermata Bus Piazza Maggiore - Telve</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC MEZZANO SANTA CROCE</t>
+          <t>IC CIVEZZANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Via Molaren, 29 – Mezzano</t>
+          <t>Park Supermercato Lidl - Civezzano</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC GIUDICARIE ESTERIORI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Piazza S. Vito 1 - Andalo</t>
+          <t>Via San Giovanni Bosco, 14 - Comano Terme</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC MORI</t>
+          <t>IC LEVICO TERME</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Via Giovanni XXIII, n. 64 – Mori</t>
+          <t>Via della Pace, 5 – Levico Terme</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC PRIMIERO</t>
+          <t>IC MEZZANO SANTA CROCE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stazione Trentino Trasporti Fiera di Primiero</t>
+          <t>Via Molaren, 29 – Mezzano</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC TRENTO 3</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Via Vittorio Veneto 61 - Trento</t>
+          <t>Piazza S. Vito 1 - Andalo</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC TRENTO 6</t>
+          <t>IC MORI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Park ex Italcementi - Trento</t>
+          <t>Via Giovanni XXIII, n. 64 – Mori</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC TRENTO 7</t>
+          <t>IC PRIMIERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Via IV Novembre 35/1 - Trento</t>
+          <t>Stazione Trentino Trasporti Fiera di Primiero</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC TRENTO 3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Piazza Palù - Madonna di Campiglio</t>
+          <t>Via Vittorio Veneto 61 - Trento</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC VALLE DEI LAGHI-DRO</t>
+          <t>IC TRENTO 6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fermata bus c/o farmacia - via Roma 3 - Vezzano</t>
+          <t>Park ex Italcementi - Trento</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC VALLE DI LEDRO</t>
+          <t>IC TRENTO 7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Via Falcone e Borsellino 2 – Bezzecca</t>
+          <t>Via IV Novembre 35/1 - Trento</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC VIGOLO VATTARO</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fermata Bus - Vigolo Vattaro</t>
+          <t>Piazza Palù - Madonna di Campiglio</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IS AGRARIO SAN MICHELE A/A</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fermata bus S. Michele, Via Biasi (dalla rotonda Conad) – San Michele A/A</t>
+          <t>Scuola Media Pinzolo, Viale della Pace 10 - Pinzolo</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IS DA VINCI</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Park ex Italcementi - Trento</t>
+          <t>Scuola Media Spiazzo, Frazione Fisto, 112 - Spiazzo</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IS DEGASPERI BORGO VALSUGANA</t>
+          <t>IC VALLE DEI LAGHI-DRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stazione intermodale est di Borgo Valsugana</t>
+          <t>Fermata bus c/o farmacia - via Roma 3 - Vezzano</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IS ENAIP TIONE</t>
+          <t>IC VALLE DI LEDRO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Via Durone n. 57, Tione</t>
+          <t>Via Falcone e Borsellino 2 – Bezzecca</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IS GALILEI TRENTO</t>
+          <t>IC VIGOLO VATTARO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Piazza Vicenza fermata autobus - Trento</t>
+          <t>Fermata Bus - Vigolo Vattaro</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IS LEVICO TERME BARELLI</t>
+          <t>IS AGRARIO SAN MICHELE A/A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Via Roma 61 – Levico Terme</t>
+          <t>Fermata bus S. Michele, Via Biasi (dalla rotonda Conad) – San Michele A/A</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IS MARCONI ROVERETO</t>
+          <t>IS DA VINCI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Via Monti 1 - Rovereto</t>
+          <t>Park ex Italcementi - Trento</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IS MARTINO MARTINI</t>
+          <t>IS DEGASPERI BORGO VALSUGANA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Via Perlasca 4 - Mezzolombardo</t>
+          <t>Stazione intermodale est di Borgo Valsugana</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IS MARTINO MARTINI – STUDENTS STAFF</t>
+          <t>IS ENAIP PRIMIERO + IS PRIMIERO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Via Perlasca 4 - Mezzolombardo</t>
+          <t>Stazione autocorriere Fiera di Primiero</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IS PERGINE VALSUGANA CURIE</t>
+          <t>IS ENAIP TIONE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Piazza Gavazzi - Pergine</t>
+          <t>Via Durone n. 57, Tione</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IS PILATI CLES</t>
+          <t>IS GALILEI TRENTO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Via IV Novembre, 35 - Cles</t>
+          <t>Piazza Vicenza fermata autobus - Trento</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IS PRIMIERO</t>
+          <t>IS LEVICO TERME BARELLI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fermata Bus Località Ponte Serra</t>
+          <t>Via Roma 61 – Levico Terme</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IS ROSA BIANCA CAVALESE</t>
+          <t>IS MARCONI ROVERETO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Corso Degasperi - Predazzo</t>
+          <t>Via Monti 1 - Rovereto</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IS ROSA BIANCA CAVALESE</t>
+          <t>IS MARTINO MARTINI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Stazione dei pullman - Cavalese</t>
+          <t>Via Perlasca 4 - Mezzolombardo</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IS ROSMINI ROVERETO</t>
+          <t>IS MARTINO MARTINI – STUDENTS STAFF</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Via Piomarta, palazzetto Sport - Rovereto</t>
+          <t>Via Perlasca 4 - Mezzolombardo</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IS ROSMINI TRENTO</t>
+          <t>IS PERGINE VALSUGANA CURIE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Via Vittorio Veneto 61 - Trento</t>
+          <t>Piazza Gavazzi - Pergine</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IS SOPHIE SCHOOL</t>
+          <t>IS PILATI CLES</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Park ex Italcementi - Trento</t>
+          <t>Via IV Novembre, 35 - Cles</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IS TESERO ENAIP</t>
+          <t>IS PRIMIERO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Via Caltrezza, 13 - Tesero</t>
+          <t>Fermata Bus Località Ponte Serra</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>IS ROSA BIANCA CAVALESE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Corso Degasperi - Predazzo</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>IS ROSA BIANCA CAVALESE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Stazione dei pullman - Cavalese</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>IS ROSMINI ROVERETO</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Via Piomarta, palazzetto Sport - Rovereto</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>IS ROSMINI TRENTO</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Via Vittorio Veneto 61 - Trento</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>IS SOPHIE SCHOOL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Park ex Italcementi - Trento</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>IS TESERO ENAIP</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Via Caltrezza, 13 - Tesero</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>IS VITTORIA BONPORTI</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Via Zambra 3 - Trento</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C45" t="n">
         <v>20</v>
       </c>
     </row>

--- a/tests/realSuite/Piano-Viaggi_Orienteering_15-aprile-2026_def/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Orienteering_15-aprile-2026_def/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,27 +436,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IC ALDENO MATTARELLO</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Via Filzi, fermata bus - Aldeno</t>
+          <t>Frazione Scancio 69 – Fermata Bus - Segonzano</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC ALDENO MATTARELLO</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Via Torre Franca – Fermata Bus "Al Parco" Mattarello</t>
+          <t>Via Negritelle 1 - Cembra</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -466,630 +466,585 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC ALTA VAL DI SOLE</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Via S. Michele, 11 – Fucine di Ossana</t>
+          <t>Via al Grec, 2 - Giovo</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC CEMBRA</t>
+          <t>IC CENTRO VALSUGANA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Frazione Scancio 69 – Fermata Bus - Segonzano</t>
+          <t>Fermata Bus "Pizzeria il Picchio" - Roncegno</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC CEMBRA</t>
+          <t>IC CENTRO VALSUGANA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Via Negritelle 1 - Cembra</t>
+          <t>Fermata Bus Piazza Maggiore - Telve</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC CEMBRA</t>
+          <t>IC CIVEZZANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Via al Grec, 2 - Giovo</t>
+          <t>Park Supermercato Lidl - Civezzano</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC CENTRO VALSUGANA</t>
+          <t>IC GIUDICARIE ESTERIORI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fermata Bus "Pizzeria il Picchio" - Roncegno</t>
+          <t>Via San Giovanni Bosco, 14 - Comano Terme</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC CENTRO VALSUGANA</t>
+          <t>IC LEVICO TERME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fermata Bus Piazza Maggiore - Telve</t>
+          <t>Via della Pace, 5 – Levico Terme</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC CIVEZZANO</t>
+          <t>IC MEZZANO SANTA CROCE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Park Supermercato Lidl - Civezzano</t>
+          <t>Via Molaren, 29 – Mezzano</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC GIUDICARIE ESTERIORI</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Via San Giovanni Bosco, 14 - Comano Terme</t>
+          <t>Piazza S. Vito 1 - Andalo</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC LEVICO TERME</t>
+          <t>IC MORI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Via della Pace, 5 – Levico Terme</t>
+          <t>Via Giovanni XXIII, n. 64 – Mori</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC MEZZANO SANTA CROCE</t>
+          <t>IC PRIMIERO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Via Molaren, 29 – Mezzano</t>
+          <t>Stazione Trentino Trasporti Fiera di Primiero</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC TRENTO 3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Piazza S. Vito 1 - Andalo</t>
+          <t>Via Vittorio Veneto 61 - Trento</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC MORI</t>
+          <t>IC TRENTO 6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Via Giovanni XXIII, n. 64 – Mori</t>
+          <t>Park ex Italcementi - Trento</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC PRIMIERO</t>
+          <t>IC TRENTO 7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stazione Trentino Trasporti Fiera di Primiero</t>
+          <t>Via IV Novembre 35/1 - Trento</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC TRENTO 3</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Via Vittorio Veneto 61 - Trento</t>
+          <t>Piazza Palù - Madonna di Campiglio</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC TRENTO 6</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Park ex Italcementi - Trento</t>
+          <t>Scuola Media Pinzolo, Viale della Pace 10 - Pinzolo</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC TRENTO 7</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Via IV Novembre 35/1 - Trento</t>
+          <t>Scuola Media Spiazzo, Frazione Fisto, 112 - Spiazzo</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC VALLE DEI LAGHI-DRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Piazza Palù - Madonna di Campiglio</t>
+          <t>Fermata bus c/o farmacia - via Roma 3 - Vezzano</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC VALLE DI LEDRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Scuola Media Pinzolo, Viale della Pace 10 - Pinzolo</t>
+          <t>Via Falcone e Borsellino 2 – Bezzecca</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC VIGOLO VATTARO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Scuola Media Spiazzo, Frazione Fisto, 112 - Spiazzo</t>
+          <t>Fermata Bus - Vigolo Vattaro</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC VALLE DEI LAGHI-DRO</t>
+          <t>IS AGRARIO SAN MICHELE A/A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fermata bus c/o farmacia - via Roma 3 - Vezzano</t>
+          <t>Fermata bus S. Michele, Via Biasi (dalla rotonda Conad) – San Michele A/A</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IC VALLE DI LEDRO</t>
+          <t>IS DA VINCI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Via Falcone e Borsellino 2 – Bezzecca</t>
+          <t>Park ex Italcementi - Trento</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC VIGOLO VATTARO</t>
+          <t>IS DEGASPERI BORGO VALSUGANA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fermata Bus - Vigolo Vattaro</t>
+          <t>Stazione intermodale est di Borgo Valsugana</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IS AGRARIO SAN MICHELE A/A</t>
+          <t>IS ENAIP PRIMIERO + IS PRIMIERO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fermata bus S. Michele, Via Biasi (dalla rotonda Conad) – San Michele A/A</t>
+          <t>Stazione autocorriere Fiera di Primiero</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IS DA VINCI</t>
+          <t>IS ENAIP TIONE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Park ex Italcementi - Trento</t>
+          <t>Via Durone n. 57, Tione</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IS DEGASPERI BORGO VALSUGANA</t>
+          <t>IS GALILEI TRENTO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Stazione intermodale est di Borgo Valsugana</t>
+          <t>Piazza Vicenza fermata autobus - Trento</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IS ENAIP PRIMIERO + IS PRIMIERO</t>
+          <t>IS LEVICO TERME BARELLI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Stazione autocorriere Fiera di Primiero</t>
+          <t>Via Roma 61 – Levico Terme</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IS ENAIP TIONE</t>
+          <t>IS MARCONI ROVERETO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Via Durone n. 57, Tione</t>
+          <t>Via Monti 1 - Rovereto</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IS GALILEI TRENTO</t>
+          <t>IS MARTINO MARTINI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Piazza Vicenza fermata autobus - Trento</t>
+          <t>Via Perlasca 4 - Mezzolombardo</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IS LEVICO TERME BARELLI</t>
+          <t>IS MARTINO MARTINI – STUDENTS STAFF</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Via Roma 61 – Levico Terme</t>
+          <t>Via Perlasca 4 - Mezzolombardo</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IS MARCONI ROVERETO</t>
+          <t>IS PERGINE VALSUGANA CURIE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Via Monti 1 - Rovereto</t>
+          <t>Piazza Gavazzi - Pergine</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IS MARTINO MARTINI</t>
+          <t>IS PILATI CLES</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Via Perlasca 4 - Mezzolombardo</t>
+          <t>Via IV Novembre, 35 - Cles</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IS MARTINO MARTINI – STUDENTS STAFF</t>
+          <t>IS PRIMIERO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Via Perlasca 4 - Mezzolombardo</t>
+          <t>Fermata Bus Località Ponte Serra</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IS PERGINE VALSUGANA CURIE</t>
+          <t>IS ROSA BIANCA CAVALESE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Piazza Gavazzi - Pergine</t>
+          <t>Corso Degasperi - Predazzo</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IS PILATI CLES</t>
+          <t>IS ROSA BIANCA CAVALESE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Via IV Novembre, 35 - Cles</t>
+          <t>Stazione dei pullman - Cavalese</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IS PRIMIERO</t>
+          <t>IS ROSMINI ROVERETO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fermata Bus Località Ponte Serra</t>
+          <t>Via Piomarta, palazzetto Sport - Rovereto</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IS ROSA BIANCA CAVALESE</t>
+          <t>IS ROSMINI TRENTO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Corso Degasperi - Predazzo</t>
+          <t>Via Vittorio Veneto 61 - Trento</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IS ROSA BIANCA CAVALESE</t>
+          <t>IS SOPHIE SCHOOL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Stazione dei pullman - Cavalese</t>
+          <t>Park ex Italcementi - Trento</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IS ROSMINI ROVERETO</t>
+          <t>IS TESERO ENAIP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Via Piomarta, palazzetto Sport - Rovereto</t>
+          <t>Via Caltrezza, 13 - Tesero</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IS ROSMINI TRENTO</t>
+          <t>IS VITTORIA BONPORTI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Via Vittorio Veneto 61 - Trento</t>
+          <t>Via Zambra 3 - Trento</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>IS SOPHIE SCHOOL</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Park ex Italcementi - Trento</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>IS TESERO ENAIP</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Via Caltrezza, 13 - Tesero</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>IS VITTORIA BONPORTI</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Via Zambra 3 - Trento</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
         <v>20</v>
       </c>
     </row>
